--- a/docs/tableau_experiences 9.xlsx
+++ b/docs/tableau_experiences 9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enrv3\Desktop\Travail\ENSAM\ENSAM 2eme année\Communication\Portfolio\Portfolio en ligne\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DDC202-86A1-4159-A492-1E49EBF49F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87733A52-7CFE-443C-9320-0ABEDACCE0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" xr2:uid="{FA858BF4-BFB0-4210-A413-73800EED7C75}"/>
   </bookViews>
